--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/capex.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/capex.xlsx
@@ -843,7 +843,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Acme Endüstri A.Ş.</t>
+          <t xml:space="preserve">Acme Endüstri A.Ş.	</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
@@ -852,7 +852,7 @@
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Teklif Numarası : 0346</t>
+          <t>Teklif Numarası : 0298</t>
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
@@ -860,7 +860,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Teklif Referans Numarası : YDD R0 06 08 2026 1 MX 1 70 25 114</t>
+          <t>Teklif Referans Numarası : YDD R0 21 09 2026 1 MX 1 76 23 112</t>
         </is>
       </c>
       <c r="B3" s="9" t="n"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>999,00 ₺</t>
+          <t>999,00 €</t>
         </is>
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
-          <t>999,00 ₺</t>
+          <t>999,00 €</t>
         </is>
       </c>
       <c r="F8" s="26" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
-          <t>879,12 ₺</t>
+          <t>879,12 €</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
-          <t>910,00 ₺</t>
+          <t>910,00 €</t>
         </is>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>910,00 ₺</t>
+          <t>910,00 €</t>
         </is>
       </c>
       <c r="F9" s="26" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="G9" s="27" t="inlineStr">
         <is>
-          <t>800,80 ₺</t>
+          <t>800,80 €</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="D10" s="26" t="inlineStr">
         <is>
-          <t>108,00 ₺</t>
+          <t>108,00 €</t>
         </is>
       </c>
       <c r="E10" s="26" t="inlineStr">
         <is>
-          <t>432,00 ₺</t>
+          <t>432,00 €</t>
         </is>
       </c>
       <c r="F10" s="26" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>380,16 ₺</t>
+          <t>380,16 €</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>Terfi Pompası (1 asil + 1 yedek) - City Pumps Ranger 10 35</t>
+          <t>Terfi Pompası (1 asil + 1 yedek)</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
-          <t>493,68 ₺</t>
+          <t>493,68 €</t>
         </is>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>987,36 ₺</t>
+          <t>987,36 €</t>
         </is>
       </c>
       <c r="F11" s="26" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
-          <t>868,88 ₺</t>
+          <t>868,88 €</t>
         </is>
       </c>
     </row>
@@ -1136,8 +1136,8 @@
           <t>PlanetDISK® MX 1 DBD Ünitesi;
 - Epoksi Boyalı AISI 1045 (C45) Karbon Çelik Dolu Mil,
 - Islak Parçalar SS304 Paslanmaz ve Galvaniz Kaplı Çelik,
-- Mil Başına 114 disk / ünite ,
-- Disk Yüzey Alanı 752,40 m² / ünite</t>
+- Mil Başına 112 disk / ünite ,
+- Disk Yüzey Alanı 739,20 m² / ünite</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
-          <t>29.625,00 ₺</t>
+          <t>29.625,00 €</t>
         </is>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>29.625,00 ₺</t>
+          <t>29.625,00 €</t>
         </is>
       </c>
       <c r="F13" s="26" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
-          <t>23.700,00 ₺</t>
+          <t>23.700,00 €</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>LS_15 Lamella Seperatör Son Çöktürme Tankı</t>
+          <t>LS_30 Lamella Seperatör Son Çöktürme Tankı</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="D14" s="26" t="inlineStr">
         <is>
-          <t>6.570,00 ₺</t>
+          <t>8.015,00 €</t>
         </is>
       </c>
       <c r="E14" s="26" t="inlineStr">
         <is>
-          <t>6.570,00 ₺</t>
+          <t>8.015,00 €</t>
         </is>
       </c>
       <c r="F14" s="26" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
-          <t>5.256,00 ₺</t>
+          <t>6.412,00 €</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
-          <t>360,36 ₺</t>
+          <t>360,36 €</t>
         </is>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>360,36 ₺</t>
+          <t>360,36 €</t>
         </is>
       </c>
       <c r="F15" s="26" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
-          <t>317,12 ₺</t>
+          <t>317,12 €</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
-          <t>3.626,00 ₺</t>
+          <t>3.626,00 €</t>
         </is>
       </c>
       <c r="E22" s="26" t="inlineStr">
         <is>
-          <t>3.626,00 ₺</t>
+          <t>3.626,00 €</t>
         </is>
       </c>
       <c r="F22" s="26" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G22" s="27" t="inlineStr">
         <is>
-          <t>3.190,88 ₺</t>
+          <t>3.190,88 €</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="D24" s="26" t="inlineStr">
         <is>
-          <t>4.897,00 ₺</t>
+          <t>4.897,00 €</t>
         </is>
       </c>
       <c r="E24" s="26" t="inlineStr">
         <is>
-          <t>4.897,00 ₺</t>
+          <t>4.897,00 €</t>
         </is>
       </c>
       <c r="F24" s="26" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G24" s="27" t="inlineStr">
         <is>
-          <t>4.309,36 ₺</t>
+          <t>4.309,36 €</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
-          <t>13.027,00 ₺</t>
+          <t>13.027,00 €</t>
         </is>
       </c>
       <c r="E26" s="28" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
-          <t>0,00 ₺</t>
+          <t>0,00 €</t>
         </is>
       </c>
       <c r="E27" s="28" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
-          <t>1.800,00 ₺</t>
+          <t>1.800,00 €</t>
         </is>
       </c>
       <c r="E29" s="26" t="inlineStr">
         <is>
-          <t>1.800,00 ₺</t>
+          <t>1.800,00 €</t>
         </is>
       </c>
       <c r="F29" s="26" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="G29" s="27" t="inlineStr">
         <is>
-          <t>1.584,00 ₺</t>
+          <t>1.584,00 €</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="D31" s="26" t="inlineStr">
         <is>
-          <t>2.300,00 ₺</t>
+          <t>2.300,00 €</t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
         <is>
-          <t>2.300,00 ₺</t>
+          <t>2.300,00 €</t>
         </is>
       </c>
       <c r="F31" s="26" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="G31" s="27" t="inlineStr">
         <is>
-          <t>2.300,00 ₺</t>
+          <t>2.300,00 €</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       <c r="D32" s="31" t="n"/>
       <c r="E32" s="32" t="inlineStr">
         <is>
-          <t>52.506,72 ₺</t>
+          <t>53.951,72 €</t>
         </is>
       </c>
       <c r="F32" s="32" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G32" s="33" t="inlineStr">
         <is>
-          <t>8.920,41 ₺</t>
+          <t>9.209,41 €</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       <c r="F33" s="31" t="n"/>
       <c r="G33" s="33" t="inlineStr">
         <is>
-          <t>43.586,31 ₺</t>
+          <t>44.742,31 €</t>
         </is>
       </c>
     </row>
